--- a/material-docente/catalogos-cfp/respuestas-ejemplo.xlsx
+++ b/material-docente/catalogos-cfp/respuestas-ejemplo.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BW7"/>
+  <dimension ref="A1:CI8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,22 +464,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Un emoji que lo represente</t>
+          <t>WhatsApp para consultas</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>WhatsApp para consultas</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>Estilo del catálogo</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Estilo del catálogo</t>
+          <t>¿Qué querés mostrar de tus productos?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -499,310 +499,370 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>Producto 1 · Otros datos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Producto 1 · Foto</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Producto 1 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Producto 2 · Nombre</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Producto 2 · Precio</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Producto 2 · Descripción</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 2 · Otros datos</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Producto 2 · Foto</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Producto 2 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Producto 3 · Nombre</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Producto 3 · Precio</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Producto 3 · Descripción</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 3 · Otros datos</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Producto 3 · Foto</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Producto 3 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Producto 4 · Nombre</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Producto 4 · Precio</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Producto 4 · Descripción</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 4 · Otros datos</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Producto 4 · Foto</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Producto 4 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Producto 5 · Nombre</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Producto 5 · Precio</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Producto 5 · Descripción</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 5 · Otros datos</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Producto 5 · Foto</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Producto 5 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Producto 6 · Nombre</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Producto 6 · Precio</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Producto 6 · Descripción</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 6 · Otros datos</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Producto 6 · Foto</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Producto 6 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Producto 7 · Nombre</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Producto 7 · Precio</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Producto 7 · Descripción</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 7 · Otros datos</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Producto 7 · Foto</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Producto 7 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>Producto 8 · Nombre</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Producto 8 · Precio</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Producto 8 · Descripción</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 8 · Otros datos</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>Producto 8 · Foto</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Producto 8 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Producto 9 · Nombre</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Producto 9 · Precio</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>Producto 9 · Descripción</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 9 · Otros datos</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Producto 9 · Foto</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Producto 9 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Producto 10 · Nombre</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>Producto 10 · Precio</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>Producto 10 · Descripción</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 10 · Otros datos</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Producto 10 · Foto</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>Producto 10 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>Producto 11 · Nombre</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>Producto 11 · Precio</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>Producto 11 · Descripción</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 11 · Otros datos</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Producto 11 · Foto</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Producto 11 · ¿Agregás otro?</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>Producto 12 · Nombre</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>Producto 12 · Precio</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>Producto 12 · Descripción</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>Producto 12 · Otros datos</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Producto 12 · Foto</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>Nombre y apellido</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>¿En qué curso del CFP estás?</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>Conformidad</t>
         </is>
       </c>
-      <c r="BU1" s="2" t="inlineStr">
+      <c r="CG1" s="2" t="inlineStr">
         <is>
           <t>Aprobado</t>
         </is>
       </c>
-      <c r="BV1" s="2" t="inlineStr">
+      <c r="CH1" s="2" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
-      <c r="BW1" s="2" t="inlineStr">
+      <c r="CI1" s="2" t="inlineStr">
         <is>
           <t>Observaciones</t>
         </is>
@@ -810,7 +870,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
-        <v>46318.58680555555</v>
+        <v>46323.58680555555</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -835,22 +895,22 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>🍯</t>
+          <t>2215550001</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2215550001</t>
+          <t>dulcesdelaisla</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>dulcesdelaisla</t>
+          <t>Dulce</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -866,87 +926,94 @@
           <t>Frasco de 500 g.</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0101</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Mermelada de frutilla</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3200</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>Con frutillas de la quinta.</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Sin TACC: sí</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0102</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Alfajores de maicena</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Por docena. Consultá por cantidades.</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0103</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>Persona de ejemplo 1</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>Pastelería</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU2" s="4" t="b">
+      <c r="CG2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="BV2" s="4" t="inlineStr">
+      <c r="CH2" s="4" t="inlineStr">
         <is>
           <t>Profe</t>
         </is>
       </c>
-      <c r="BW2" s="4" t="inlineStr"/>
+      <c r="CI2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
-        <v>46318.65277777778</v>
+        <v>46323.65277777778</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -967,18 +1034,18 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>🧶</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
           <t>2215550002</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Natural</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Natural</t>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -991,66 +1058,77 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Talle único. Varios colores.</t>
+          <t>Varios colores.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>Talles: S, M y L
+Material: lana de oveja</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0201</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Bufanda</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>9500</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Largo: 1,60 m</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0202</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>Persona de ejemplo 2</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>Pensamiento Computacional</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU3" s="4" t="b">
+      <c r="CG3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="BV3" s="4" t="inlineStr">
+      <c r="CH3" s="4" t="inlineStr">
         <is>
           <t>Preceptoría</t>
         </is>
       </c>
-      <c r="BW3" s="4" t="inlineStr"/>
+      <c r="CI3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46319.42708333334</v>
+        <v>46324.38194444445</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1059,87 +1137,116 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>La Vela Encendida</t>
+          <t>Impresiones 3D Ensenada</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Velas aromáticas</t>
+          <t>Impresión 3D</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Velas de soja con esencias naturales.</t>
+          <t>Piezas a medida y objetos de diseño.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>🕯️</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2215550003</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>2215550004</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Mar</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Descripción, Foto</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Vela de lavanda</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>4200</v>
+          <t>Maceta geométrica</t>
+        </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dura 30 horas.</t>
+          <t>Para suculentas.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
+          <t>Material: PLA biodegradable
+Medidas: 10 x 10 x 12 cm
+Colores: blanco, verde o terracota</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0301</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Llavero con tu nombre</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Con el nombre que quieras.</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Tiempo de entrega: 3 días</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=EJEMPLO-0302</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>Persona de ejemplo 3</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>Auxiliar en Cosmética</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>Pensamiento Computacional</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU4" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BV4" s="4" t="inlineStr"/>
-      <c r="BW4" s="4" t="inlineStr">
-        <is>
-          <t>Falta revisar las fotos</t>
-        </is>
-      </c>
+      <c r="CG4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH4" s="4" t="inlineStr">
+        <is>
+          <t>Profe</t>
+        </is>
+      </c>
+      <c r="CI4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46320.39583333334</v>
+        <v>46324.42708333334</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1148,153 +1255,88 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dulces de la Isla</t>
+          <t>La Vela Encendida</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dulces caseros</t>
+          <t>Velas aromáticas</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dulce de leche y mermeladas hechas en la Isla Santiago.</t>
+          <t>Velas de soja con esencias naturales.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>🍯</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2215550001</t>
-        </is>
-      </c>
+          <t>2215550003</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dulcesdelaisla</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dulce</t>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Dulce de leche casero</t>
+          <t>Vela de lavanda</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Frasco de 500 g.</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+          <t>Dura 30 horas.</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0401</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mermelada de frutilla</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>3200</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Con frutillas de la quinta.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/open?id=EJEMPLO-0402</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Alfajores de maicena</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Por docena.</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/open?id=EJEMPLO-0403</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Pastafrola</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>6000</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>De membrillo o de batata.</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/open?id=EJEMPLO-0404</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>Persona de ejemplo 4</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>Pastelería</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>Auxiliar en Cosmética</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU5" s="4" t="b">
+      <c r="CG5" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="BV5" s="4" t="inlineStr"/>
-      <c r="BW5" s="4" t="inlineStr"/>
+      <c r="CH5" s="4" t="inlineStr"/>
+      <c r="CI5" s="4" t="inlineStr">
+        <is>
+          <t>Falta revisar las fotos</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46320.45833333334</v>
+        <v>46325.39583333334</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1303,83 +1345,112 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mates del Río</t>
+          <t>Dulces de la Isla</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mates y bombillas</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>Dulces caseros</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dulce de leche y mermeladas hechas en la Isla Santiago.</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>🧉</t>
+          <t>2215550001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>221555</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>dulcesdelaisla</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Dulce</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Elegante</t>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Mate de calabaza</t>
+          <t>Dulce de leche casero</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7800</v>
+        <v>3800</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Curado y listo para usar.</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
+          <t>Frasco de 500 g.</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://drive.google.com/open?id=EJEMPLO-0501</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Pastafrola</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>6000</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>De membrillo o de batata.</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=EJEMPLO-0502</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>Persona de ejemplo 5</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>Marroquinería</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>Pastelería</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="BV6" s="4" t="inlineStr">
-        <is>
-          <t>Profe</t>
-        </is>
-      </c>
-      <c r="BW6" s="4" t="inlineStr"/>
+      <c r="CG6" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH6" s="4" t="inlineStr"/>
+      <c r="CI6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46320.51388888889</v>
+        <v>46325.45833333334</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1388,110 +1459,202 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bijou Ensenada</t>
+          <t>Mates del Río</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bijouterie</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>&lt;script&gt;alert('hola')&lt;/script&gt;</t>
-        </is>
-      </c>
+          <t>Mates y bombillas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>💍</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+          <t>221555</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Elegante</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Mate de calabaza</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>7800</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Curado y listo para usar.</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=EJEMPLO-0601</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>Persona de ejemplo 6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>Marroquinería</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
+        </is>
+      </c>
+      <c r="CG7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH7" s="4" t="inlineStr">
+        <is>
+          <t>Profe</t>
+        </is>
+      </c>
+      <c r="CI7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>46325.51388888889</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>persona7@example.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Bijou Ensenada</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bijouterie</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>&lt;script&gt;alert('hola')&lt;/script&gt;</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
         <is>
           <t>2215550005</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>@bijou.ensenada</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Alegre</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Precio, Descripción, Foto, Un botón de WhatsApp en cada producto</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>Aros de acero</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" t="n">
         <v>2500</v>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Hipoalergénicos.</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/open?id=EJEMPLO-0601</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;Oferta&lt;/b&gt;: &lt;img src=x onerror=alert(1)&gt;</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=EJEMPLO-0701</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Pulsera tejida</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R8" t="n">
         <v>1800</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>&lt;b&gt;en negrita?&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/open?id=EJEMPLO-0602</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://drive.google.com/open?id=EJEMPLO-0702</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>Persona de ejemplo 6</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>Persona de ejemplo 7</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
         <is>
           <t>Pensamiento Computacional</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>Acepto que los datos del emprendimiento se publiquen en internet en un catálogo del CFP 401. Mi nombre y mi curso no se publican., Las fotos son mías o tengo permiso para usarlas., Entiendo que alguien del CFP lo revisa antes de publicarlo, y que puedo pedir que lo den de baja cuando quiera.</t>
         </is>
       </c>
-      <c r="BU7" s="4" t="b">
+      <c r="CG8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="BV7" s="4" t="inlineStr">
+      <c r="CH8" s="4" t="inlineStr">
         <is>
           <t>Profe</t>
         </is>
       </c>
-      <c r="BW7" s="4" t="inlineStr"/>
+      <c r="CI8" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
